--- a/bom/BOM_Three_Phase_Driver_VER2.2.xlsx
+++ b/bom/BOM_Three_Phase_Driver_VER2.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EV-TECH\Desktop\Проекты\Three-Phase-80kWt\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E997401-C3F2-4563-9632-2FEF6902D8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E006BA7-E882-46FA-A84C-D222611C7165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="126">
   <si>
     <t>Reference</t>
   </si>
@@ -88,7 +88,7 @@
     <t>10n</t>
   </si>
   <si>
-    <t>C30,C45,C46,C54,C59,C60,C65,C66,C71,C72,C79,C82,C83,C86,C87</t>
+    <t>C30,C45,C46,C54,C59,C60,C65,C66,C71,C72,C79,C82,C83,C86,C87,C96,C97,C98,C99,C100,C101</t>
   </si>
   <si>
     <t>56p</t>
@@ -109,12 +109,12 @@
     <t>C90,C91,C92,C93,C94,C95</t>
   </si>
   <si>
+    <t>~</t>
+  </si>
+  <si>
     <t>D1,D23,D25</t>
   </si>
   <si>
-    <t>~</t>
-  </si>
-  <si>
     <t>SN74AHC1G08DBVR</t>
   </si>
   <si>
@@ -235,6 +235,9 @@
     <t>J3,J4,J5</t>
   </si>
   <si>
+    <t>SCT3001WV-2x06P</t>
+  </si>
+  <si>
     <t>Connector</t>
   </si>
   <si>
@@ -250,6 +253,9 @@
     <t>LQH32MN120J23L</t>
   </si>
   <si>
+    <t>Inductor SMD</t>
+  </si>
+  <si>
     <t>Inductor_SMD:L_1210_3225Metric_Pad1.42x2.65mm_HandSolder</t>
   </si>
   <si>
@@ -265,6 +271,18 @@
     <t>Inductor_SMD:L_1812_4532Metric_Pad1.30x3.40mm_HandSolder</t>
   </si>
   <si>
+    <t>L13,L14,L15,L16,L17,L18,L19,L20,L21,L22,L23,L24</t>
+  </si>
+  <si>
+    <t>1u</t>
+  </si>
+  <si>
+    <t>MLZ1608A1R0WT000</t>
+  </si>
+  <si>
+    <t>Inductor_SMD:L_0603_1608Metric_Pad1.05x0.95mm_HandSolder</t>
+  </si>
+  <si>
     <t>Q1,Q2,Q3</t>
   </si>
   <si>
@@ -376,20 +394,17 @@
     <t>Digital Isolator</t>
   </si>
   <si>
+    <t>Resistor SMD</t>
+  </si>
+  <si>
     <t>Capacitor 25V+</t>
-  </si>
-  <si>
-    <t>Resistor SMD</t>
-  </si>
-  <si>
-    <t>Inductor SMD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -402,13 +417,27 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -438,12 +467,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -750,43 +782,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" customWidth="1"/>
-    <col min="3" max="3" width="28.109375" customWidth="1"/>
-    <col min="4" max="4" width="26.21875" customWidth="1"/>
-    <col min="5" max="5" width="21.44140625" customWidth="1"/>
-    <col min="6" max="6" width="21.109375" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="3" max="3" width="25.88671875" customWidth="1"/>
+    <col min="4" max="4" width="19.21875" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="23.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -796,7 +829,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>10</v>
@@ -806,7 +839,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -816,7 +849,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>13</v>
@@ -836,7 +869,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>16</v>
@@ -856,7 +889,7 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
@@ -876,7 +909,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>10</v>
@@ -896,7 +929,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>10</v>
@@ -906,7 +939,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -916,13 +949,13 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="1">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H8" s="1"/>
     </row>
@@ -936,7 +969,7 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>13</v>
@@ -956,7 +989,7 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>10</v>
@@ -971,12 +1004,12 @@
         <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>10</v>
@@ -984,14 +1017,16 @@
       <c r="G11" s="1">
         <v>6</v>
       </c>
-      <c r="H11" s="1"/>
+      <c r="H11" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>31</v>
@@ -1013,7 +1048,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>35</v>
@@ -1035,7 +1070,7 @@
         <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>39</v>
@@ -1057,7 +1092,7 @@
         <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>43</v>
@@ -1079,7 +1114,7 @@
         <v>46</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>47</v>
@@ -1101,7 +1136,7 @@
         <v>50</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>51</v>
@@ -1123,7 +1158,7 @@
         <v>53</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>54</v>
@@ -1145,7 +1180,7 @@
         <v>56</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>57</v>
@@ -1167,7 +1202,7 @@
         <v>60</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>61</v>
@@ -1189,7 +1224,7 @@
         <v>64</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>65</v>
@@ -1211,7 +1246,7 @@
         <v>66</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>67</v>
@@ -1233,376 +1268,400 @@
         <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G23" s="1">
         <v>3</v>
       </c>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" s="1"/>
-      <c r="E24" s="2" t="s">
-        <v>120</v>
+      <c r="E24" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G24" s="1">
         <v>6</v>
       </c>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="F25" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G25" s="1">
         <v>6</v>
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G26" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H26" s="1"/>
     </row>
     <row r="27" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B27" s="1">
+        <v>87</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="1">
+        <v>3</v>
+      </c>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="1">
         <v>120</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G27" s="1">
-        <v>18</v>
-      </c>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="1">
-        <v>0</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G28" s="1">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B29" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G29" s="1">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
+      </c>
+      <c r="B30" s="1">
+        <v>10</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G30" s="1">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G31" s="1">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G32" s="1">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G33" s="1">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H33" s="1"/>
     </row>
     <row r="34" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G34" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H34" s="1"/>
     </row>
     <row r="35" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G35" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B36" s="1">
-        <v>560</v>
+        <v>106</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G36" s="1">
+        <v>3</v>
+      </c>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="1">
+        <v>560</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G37" s="1">
         <v>12</v>
       </c>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G37" s="1">
-        <v>1</v>
-      </c>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G38" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H38" s="1"/>
     </row>
     <row r="39" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G39" s="1">
         <v>3</v>
       </c>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>116</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="D40" s="1"/>
       <c r="E40" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="G40" s="1">
         <v>3</v>
       </c>
       <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G41" s="1">
+        <v>3</v>
+      </c>
+      <c r="H41" s="1"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
